--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>97791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R2" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B3" t="n">
-        <v>97791</v>
+        <v>57016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R3" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1109,53 +1109,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130340200</v>
+        <v>130341476</v>
       </c>
       <c r="B6" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510881</v>
+        <v>510780</v>
       </c>
       <c r="R6" t="n">
-        <v>6746060</v>
+        <v>6746239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,19 +1177,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,57 +1194,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341476</v>
+        <v>130340200</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510780</v>
+        <v>510881</v>
       </c>
       <c r="R7" t="n">
-        <v>6746239</v>
+        <v>6746060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,9 +1282,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,60 +1309,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R8" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,98 +1397,77 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B9" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R9" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,29 +1497,45 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130340199</v>
+        <v>130334045</v>
       </c>
       <c r="B19" t="n">
-        <v>57016</v>
+        <v>97791</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,42 +2524,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510881</v>
+        <v>510878</v>
       </c>
       <c r="R19" t="n">
-        <v>6746053</v>
+        <v>6746081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,12 +2608,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2735,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130334045</v>
+        <v>130340199</v>
       </c>
       <c r="B21" t="n">
-        <v>97791</v>
+        <v>57016</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,34 +2738,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510878</v>
+        <v>510881</v>
       </c>
       <c r="R21" t="n">
-        <v>6746081</v>
+        <v>6746053</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,12 +2830,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3056,45 +3056,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341475</v>
+        <v>130342664</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>97797</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511192</v>
+        <v>510904</v>
       </c>
       <c r="R24" t="n">
-        <v>6746313</v>
+        <v>6746037</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,9 +3124,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,57 +3151,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130342664</v>
+        <v>130341475</v>
       </c>
       <c r="B25" t="n">
-        <v>97797</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510904</v>
+        <v>511192</v>
       </c>
       <c r="R25" t="n">
-        <v>6746037</v>
+        <v>6746313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,19 +3231,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,15 +3248,408 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130347969</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Grissbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>510838</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6746064</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130347955</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57016</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Grissbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>510724</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6745987</v>
+      </c>
+      <c r="S27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130347959</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97797</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Grissbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>510858</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6746017</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>20 m3</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130347968</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79180</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Grissbäcken, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>510802</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6746015</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erik Danielsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B2" t="n">
-        <v>97791</v>
+        <v>57016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R2" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +778,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>57016</v>
+        <v>97791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R3" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1321,53 +1321,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B8" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R8" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,77 +1392,98 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R9" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,45 +1513,29 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B11" t="n">
-        <v>97791</v>
+        <v>57016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,34 +1665,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R11" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1757,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>57016</v>
+        <v>97791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,42 +1780,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R12" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,22 +1864,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130342663</v>
+        <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97791</v>
+        <v>97797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,16 +1887,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1907,14 +1907,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510579</v>
+        <v>510871</v>
       </c>
       <c r="R13" t="n">
-        <v>6746019</v>
+        <v>6746071</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,22 +1971,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130334004</v>
+        <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97797</v>
+        <v>97791</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,16 +1994,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2014,14 +2014,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510871</v>
+        <v>510579</v>
       </c>
       <c r="R14" t="n">
-        <v>6746071</v>
+        <v>6746019</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,12 +2078,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2842,10 +2842,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130332893</v>
+        <v>130340205</v>
       </c>
       <c r="B22" t="n">
-        <v>97791</v>
+        <v>97797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2853,16 +2853,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2873,14 +2873,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510545</v>
+        <v>510865</v>
       </c>
       <c r="R22" t="n">
-        <v>6746173</v>
+        <v>6746076</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,22 +2937,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130340205</v>
+        <v>130332893</v>
       </c>
       <c r="B23" t="n">
-        <v>97797</v>
+        <v>97791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,16 +2960,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2980,14 +2980,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510865</v>
+        <v>510545</v>
       </c>
       <c r="R23" t="n">
-        <v>6746076</v>
+        <v>6746173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,57 +3044,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130342664</v>
+        <v>130341475</v>
       </c>
       <c r="B24" t="n">
-        <v>97797</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510904</v>
+        <v>511192</v>
       </c>
       <c r="R24" t="n">
-        <v>6746037</v>
+        <v>6746313</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,19 +3124,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,57 +3141,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130341475</v>
+        <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>97797</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511192</v>
+        <v>510904</v>
       </c>
       <c r="R25" t="n">
-        <v>6746313</v>
+        <v>6746037</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,9 +3221,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,12 +3248,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -1321,48 +1321,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R8" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,98 +1397,77 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B9" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R9" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,29 +1497,45 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B11" t="n">
-        <v>97791</v>
+        <v>57016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,34 +1665,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R11" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1757,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>57016</v>
+        <v>97791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,42 +1780,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R12" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B11" t="n">
-        <v>57016</v>
+        <v>97791</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,42 +1665,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R11" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,22 +1749,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B12" t="n">
-        <v>97791</v>
+        <v>57016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,34 +1772,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R12" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -1321,53 +1321,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B8" t="n">
-        <v>57016</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R8" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,77 +1392,98 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B9" t="n">
-        <v>79180</v>
+        <v>57016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R9" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,45 +1513,29 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B11" t="n">
-        <v>97791</v>
+        <v>57016</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,34 +1665,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R11" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1757,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>57016</v>
+        <v>97791</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,42 +1780,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R12" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>130340203</v>
       </c>
       <c r="B4" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>130341476</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>130340207</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>130334159</v>
       </c>
       <c r="B15" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130340204</v>
+        <v>130334085</v>
       </c>
       <c r="B16" t="n">
-        <v>97797</v>
+        <v>57016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,34 +2208,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510879</v>
+        <v>510869</v>
       </c>
       <c r="R16" t="n">
-        <v>6746058</v>
+        <v>6746060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2272,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,7 +2282,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2292,22 +2297,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130334085</v>
+        <v>130340204</v>
       </c>
       <c r="B17" t="n">
-        <v>57016</v>
+        <v>97800</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,39 +2320,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510869</v>
+        <v>510879</v>
       </c>
       <c r="R17" t="n">
-        <v>6746060</v>
+        <v>6746058</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,12 +2404,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2419,7 +2419,7 @@
         <v>130341468</v>
       </c>
       <c r="B18" t="n">
-        <v>97794</v>
+        <v>97797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>130334045</v>
       </c>
       <c r="B20" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130333964</v>
       </c>
       <c r="B21" t="n">
-        <v>97794</v>
+        <v>97797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130340205</v>
       </c>
       <c r="B22" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>130332893</v>
       </c>
       <c r="B23" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>130341475</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>130347969</v>
       </c>
       <c r="B26" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97797</v>
+        <v>97800</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>130347968</v>
       </c>
       <c r="B29" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>97820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R2" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B3" t="n">
-        <v>97794</v>
+        <v>57042</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R3" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -900,7 +900,7 @@
         <v>130340203</v>
       </c>
       <c r="B4" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130341464</v>
       </c>
       <c r="B5" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>130341476</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>130340200</v>
       </c>
       <c r="B7" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>130340207</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>130341465</v>
       </c>
       <c r="B9" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>130334033</v>
       </c>
       <c r="B10" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130342662</v>
       </c>
       <c r="B11" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>130334159</v>
       </c>
       <c r="B15" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>130334085</v>
       </c>
       <c r="B16" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>130340204</v>
       </c>
       <c r="B17" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130341468</v>
       </c>
       <c r="B18" t="n">
-        <v>97797</v>
+        <v>97823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>130340199</v>
       </c>
       <c r="B19" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>130334045</v>
       </c>
       <c r="B20" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130333964</v>
       </c>
       <c r="B21" t="n">
-        <v>97797</v>
+        <v>97823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130340205</v>
       </c>
       <c r="B22" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>130332893</v>
       </c>
       <c r="B23" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>130341475</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>130347969</v>
       </c>
       <c r="B26" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>130347955</v>
       </c>
       <c r="B27" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97800</v>
+        <v>97826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>130347968</v>
       </c>
       <c r="B29" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B2" t="n">
-        <v>97820</v>
+        <v>57042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R2" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +778,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>57042</v>
+        <v>97821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R3" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -900,7 +900,7 @@
         <v>130340203</v>
       </c>
       <c r="B4" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1321,48 +1321,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R8" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,98 +1397,77 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B9" t="n">
-        <v>57042</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R9" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,29 +1497,45 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
         <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>130334159</v>
       </c>
       <c r="B15" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>130340204</v>
       </c>
       <c r="B17" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130341468</v>
       </c>
       <c r="B18" t="n">
-        <v>97823</v>
+        <v>97824</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>130334045</v>
       </c>
       <c r="B20" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130333964</v>
       </c>
       <c r="B21" t="n">
-        <v>97823</v>
+        <v>97824</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130340205</v>
       </c>
       <c r="B22" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>130332893</v>
       </c>
       <c r="B23" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97826</v>
+        <v>97827</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>130340203</v>
       </c>
       <c r="B4" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1109,45 +1109,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130341476</v>
+        <v>130340200</v>
       </c>
       <c r="B6" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510780</v>
+        <v>510881</v>
       </c>
       <c r="R6" t="n">
-        <v>6746239</v>
+        <v>6746060</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,9 +1185,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,65 +1212,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130340200</v>
+        <v>130341476</v>
       </c>
       <c r="B7" t="n">
-        <v>57042</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510881</v>
+        <v>510780</v>
       </c>
       <c r="R7" t="n">
-        <v>6746060</v>
+        <v>6746239</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,19 +1292,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,65 +1309,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B8" t="n">
-        <v>57042</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R8" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,77 +1392,98 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>57042</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R9" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,45 +1513,29 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
         <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>130334159</v>
       </c>
       <c r="B15" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130334085</v>
+        <v>130340204</v>
       </c>
       <c r="B16" t="n">
-        <v>57042</v>
+        <v>97828</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,39 +2208,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510869</v>
+        <v>510879</v>
       </c>
       <c r="R16" t="n">
-        <v>6746060</v>
+        <v>6746058</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,7 +2267,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2282,7 +2277,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,22 +2292,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130340204</v>
+        <v>130334085</v>
       </c>
       <c r="B17" t="n">
-        <v>97827</v>
+        <v>57042</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,34 +2315,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510879</v>
+        <v>510869</v>
       </c>
       <c r="R17" t="n">
-        <v>6746058</v>
+        <v>6746060</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,12 +2404,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2419,7 +2419,7 @@
         <v>130341468</v>
       </c>
       <c r="B18" t="n">
-        <v>97824</v>
+        <v>97825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130334045</v>
+        <v>130333964</v>
       </c>
       <c r="B20" t="n">
-        <v>97821</v>
+        <v>97825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510878</v>
+        <v>510858</v>
       </c>
       <c r="R20" t="n">
-        <v>6746081</v>
+        <v>6746074</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130333964</v>
+        <v>130334045</v>
       </c>
       <c r="B21" t="n">
-        <v>97824</v>
+        <v>97822</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,16 +2746,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510858</v>
+        <v>510878</v>
       </c>
       <c r="R21" t="n">
-        <v>6746074</v>
+        <v>6746081</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130340205</v>
+        <v>130332893</v>
       </c>
       <c r="B22" t="n">
-        <v>97827</v>
+        <v>97822</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2853,16 +2853,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2873,14 +2873,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510865</v>
+        <v>510545</v>
       </c>
       <c r="R22" t="n">
-        <v>6746076</v>
+        <v>6746173</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,22 +2937,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130332893</v>
+        <v>130340205</v>
       </c>
       <c r="B23" t="n">
-        <v>97821</v>
+        <v>97828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,16 +2960,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2980,14 +2980,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510545</v>
+        <v>510865</v>
       </c>
       <c r="R23" t="n">
-        <v>6746173</v>
+        <v>6746076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,12 +3044,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3156,7 +3156,7 @@
         <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97827</v>
+        <v>97828</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130340201</v>
       </c>
       <c r="B2" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>130340203</v>
       </c>
       <c r="B4" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130341464</v>
       </c>
       <c r="B5" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,53 +1109,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130340200</v>
+        <v>130341476</v>
       </c>
       <c r="B6" t="n">
-        <v>57042</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510881</v>
+        <v>510780</v>
       </c>
       <c r="R6" t="n">
-        <v>6746060</v>
+        <v>6746239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,19 +1177,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,57 +1194,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341476</v>
+        <v>130340200</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>57044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510780</v>
+        <v>510881</v>
       </c>
       <c r="R7" t="n">
-        <v>6746239</v>
+        <v>6746060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,9 +1282,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,12 +1309,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1324,7 +1324,7 @@
         <v>130340207</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>130341465</v>
       </c>
       <c r="B9" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>130334033</v>
       </c>
       <c r="B10" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130342662</v>
       </c>
       <c r="B11" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>130334159</v>
       </c>
       <c r="B15" t="n">
-        <v>97822</v>
+        <v>97824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>130340204</v>
       </c>
       <c r="B16" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>130334085</v>
       </c>
       <c r="B17" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130341468</v>
       </c>
       <c r="B18" t="n">
-        <v>97825</v>
+        <v>97827</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>130340199</v>
       </c>
       <c r="B19" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130333964</v>
+        <v>130334045</v>
       </c>
       <c r="B20" t="n">
-        <v>97825</v>
+        <v>97824</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,16 +2639,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510858</v>
+        <v>510878</v>
       </c>
       <c r="R20" t="n">
-        <v>6746074</v>
+        <v>6746081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130334045</v>
+        <v>130333964</v>
       </c>
       <c r="B21" t="n">
-        <v>97822</v>
+        <v>97827</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,16 +2746,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510878</v>
+        <v>510858</v>
       </c>
       <c r="R21" t="n">
-        <v>6746081</v>
+        <v>6746074</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,10 +2842,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130332893</v>
+        <v>130340205</v>
       </c>
       <c r="B22" t="n">
-        <v>97822</v>
+        <v>97830</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2853,16 +2853,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2873,14 +2873,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510545</v>
+        <v>510865</v>
       </c>
       <c r="R22" t="n">
-        <v>6746173</v>
+        <v>6746076</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,22 +2937,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130340205</v>
+        <v>130332893</v>
       </c>
       <c r="B23" t="n">
-        <v>97828</v>
+        <v>97824</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,16 +2960,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2980,14 +2980,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510865</v>
+        <v>510545</v>
       </c>
       <c r="R23" t="n">
-        <v>6746076</v>
+        <v>6746173</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,12 +3044,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3059,7 +3059,7 @@
         <v>130341475</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>130347969</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>130347955</v>
       </c>
       <c r="B27" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97828</v>
+        <v>97830</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>130347968</v>
       </c>
       <c r="B29" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>130340203</v>
       </c>
       <c r="B4" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1321,48 +1321,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R8" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,98 +1397,77 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B9" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R9" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,29 +1497,45 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
         <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>130334159</v>
       </c>
       <c r="B15" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130340204</v>
+        <v>130334085</v>
       </c>
       <c r="B16" t="n">
-        <v>97830</v>
+        <v>57044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,34 +2208,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510879</v>
+        <v>510869</v>
       </c>
       <c r="R16" t="n">
-        <v>6746058</v>
+        <v>6746060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2272,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,7 +2282,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2292,22 +2297,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130334085</v>
+        <v>130340204</v>
       </c>
       <c r="B17" t="n">
-        <v>57044</v>
+        <v>97834</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,39 +2320,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510869</v>
+        <v>510879</v>
       </c>
       <c r="R17" t="n">
-        <v>6746060</v>
+        <v>6746058</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,12 +2404,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2419,7 +2419,7 @@
         <v>130341468</v>
       </c>
       <c r="B18" t="n">
-        <v>97827</v>
+        <v>97831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130340199</v>
+        <v>130334045</v>
       </c>
       <c r="B19" t="n">
-        <v>57044</v>
+        <v>97828</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,42 +2524,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510881</v>
+        <v>510878</v>
       </c>
       <c r="R19" t="n">
-        <v>6746053</v>
+        <v>6746081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,22 +2608,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130334045</v>
+        <v>130333964</v>
       </c>
       <c r="B20" t="n">
-        <v>97824</v>
+        <v>97831</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,16 +2631,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2663,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510878</v>
+        <v>510858</v>
       </c>
       <c r="R20" t="n">
-        <v>6746081</v>
+        <v>6746074</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130333964</v>
+        <v>130340199</v>
       </c>
       <c r="B21" t="n">
-        <v>97827</v>
+        <v>57044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,34 +2738,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510858</v>
+        <v>510881</v>
       </c>
       <c r="R21" t="n">
-        <v>6746074</v>
+        <v>6746053</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,12 +2830,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2845,7 +2845,7 @@
         <v>130340205</v>
       </c>
       <c r="B22" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>130332893</v>
       </c>
       <c r="B23" t="n">
-        <v>97824</v>
+        <v>97828</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97830</v>
+        <v>97834</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>97828</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R2" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B3" t="n">
-        <v>97828</v>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R3" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1321,53 +1321,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B8" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R8" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,77 +1392,98 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B9" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R9" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,45 +1513,29 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B11" t="n">
-        <v>57044</v>
+        <v>97828</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,42 +1665,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R11" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,22 +1749,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B12" t="n">
-        <v>97828</v>
+        <v>57044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,34 +1772,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R12" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130334045</v>
+        <v>130340199</v>
       </c>
       <c r="B19" t="n">
-        <v>97828</v>
+        <v>57044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,34 +2524,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510878</v>
+        <v>510881</v>
       </c>
       <c r="R19" t="n">
-        <v>6746081</v>
+        <v>6746053</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2593,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,22 +2616,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130333964</v>
+        <v>130334045</v>
       </c>
       <c r="B20" t="n">
-        <v>97831</v>
+        <v>97828</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,16 +2639,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2655,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510858</v>
+        <v>510878</v>
       </c>
       <c r="R20" t="n">
-        <v>6746074</v>
+        <v>6746081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2727,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130340199</v>
+        <v>130333964</v>
       </c>
       <c r="B21" t="n">
-        <v>57044</v>
+        <v>97831</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,42 +2746,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510881</v>
+        <v>510858</v>
       </c>
       <c r="R21" t="n">
-        <v>6746053</v>
+        <v>6746074</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,12 +2830,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3056,45 +3056,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341475</v>
+        <v>130342664</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>97834</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511192</v>
+        <v>510904</v>
       </c>
       <c r="R24" t="n">
-        <v>6746313</v>
+        <v>6746037</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,9 +3124,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,57 +3151,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130342664</v>
+        <v>130341475</v>
       </c>
       <c r="B25" t="n">
-        <v>97834</v>
+        <v>79211</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510904</v>
+        <v>511192</v>
       </c>
       <c r="R25" t="n">
-        <v>6746037</v>
+        <v>6746313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,19 +3231,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,12 +3248,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B2" t="n">
-        <v>97828</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R2" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +778,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>97828</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R3" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B11" t="n">
-        <v>97828</v>
+        <v>57044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,34 +1665,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R11" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1757,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>57044</v>
+        <v>97828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,42 +1780,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R12" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3056,45 +3056,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130342664</v>
+        <v>130341475</v>
       </c>
       <c r="B24" t="n">
-        <v>97834</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510904</v>
+        <v>511192</v>
       </c>
       <c r="R24" t="n">
-        <v>6746037</v>
+        <v>6746313</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,19 +3124,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,57 +3141,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130341475</v>
+        <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>97834</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511192</v>
+        <v>510904</v>
       </c>
       <c r="R25" t="n">
-        <v>6746313</v>
+        <v>6746037</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,9 +3221,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,12 +3248,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -1109,45 +1109,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130341476</v>
+        <v>130340200</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>57044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510780</v>
+        <v>510881</v>
       </c>
       <c r="R6" t="n">
-        <v>6746239</v>
+        <v>6746060</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,9 +1185,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,65 +1212,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130340200</v>
+        <v>130341476</v>
       </c>
       <c r="B7" t="n">
-        <v>57044</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510881</v>
+        <v>510780</v>
       </c>
       <c r="R7" t="n">
-        <v>6746060</v>
+        <v>6746239</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,19 +1292,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,12 +1309,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B11" t="n">
-        <v>57044</v>
+        <v>97828</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,42 +1665,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R11" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,22 +1749,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B12" t="n">
-        <v>97828</v>
+        <v>57044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,34 +1772,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R12" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>97841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R2" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B3" t="n">
-        <v>97828</v>
+        <v>57052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R3" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -900,7 +900,7 @@
         <v>130340203</v>
       </c>
       <c r="B4" t="n">
-        <v>97834</v>
+        <v>97847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130341464</v>
       </c>
       <c r="B5" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,53 +1109,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130340200</v>
+        <v>130341476</v>
       </c>
       <c r="B6" t="n">
-        <v>57044</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510881</v>
+        <v>510780</v>
       </c>
       <c r="R6" t="n">
-        <v>6746060</v>
+        <v>6746239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,19 +1177,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,57 +1194,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341476</v>
+        <v>130340200</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>57052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510780</v>
+        <v>510881</v>
       </c>
       <c r="R7" t="n">
-        <v>6746239</v>
+        <v>6746060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,9 +1282,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,60 +1309,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>57052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R8" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,98 +1397,77 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B9" t="n">
-        <v>57044</v>
+        <v>79219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R9" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,29 +1497,45 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
         <v>130334033</v>
       </c>
       <c r="B10" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B11" t="n">
-        <v>97828</v>
+        <v>57052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,34 +1665,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R11" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1757,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>57044</v>
+        <v>97841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,42 +1780,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R12" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
         <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97834</v>
+        <v>97847</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>130334159</v>
       </c>
       <c r="B15" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>130334085</v>
       </c>
       <c r="B16" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>130340204</v>
       </c>
       <c r="B17" t="n">
-        <v>97834</v>
+        <v>97847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130341468</v>
       </c>
       <c r="B18" t="n">
-        <v>97831</v>
+        <v>97844</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>130340199</v>
       </c>
       <c r="B19" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>130334045</v>
       </c>
       <c r="B20" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130333964</v>
       </c>
       <c r="B21" t="n">
-        <v>97831</v>
+        <v>97844</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130340205</v>
       </c>
       <c r="B22" t="n">
-        <v>97834</v>
+        <v>97847</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>130332893</v>
       </c>
       <c r="B23" t="n">
-        <v>97828</v>
+        <v>97841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>130341475</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>97834</v>
+        <v>97847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>130347969</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>130347955</v>
       </c>
       <c r="B27" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97834</v>
+        <v>97847</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>130347968</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B2" t="n">
-        <v>97841</v>
+        <v>57053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R2" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +778,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>57052</v>
+        <v>97842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R3" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -900,7 +900,7 @@
         <v>130340203</v>
       </c>
       <c r="B4" t="n">
-        <v>97847</v>
+        <v>97848</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130341464</v>
       </c>
       <c r="B5" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,45 +1109,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130341476</v>
+        <v>130340200</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510780</v>
+        <v>510881</v>
       </c>
       <c r="R6" t="n">
-        <v>6746239</v>
+        <v>6746060</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,9 +1185,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,65 +1212,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130340200</v>
+        <v>130341476</v>
       </c>
       <c r="B7" t="n">
-        <v>57052</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510881</v>
+        <v>510780</v>
       </c>
       <c r="R7" t="n">
-        <v>6746060</v>
+        <v>6746239</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,19 +1292,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,12 +1309,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1324,7 +1324,7 @@
         <v>130341465</v>
       </c>
       <c r="B8" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>130340207</v>
       </c>
       <c r="B9" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>130334033</v>
       </c>
       <c r="B10" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>130342662</v>
       </c>
       <c r="B11" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97847</v>
+        <v>97848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>130334159</v>
       </c>
       <c r="B15" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>130334085</v>
       </c>
       <c r="B16" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>130340204</v>
       </c>
       <c r="B17" t="n">
-        <v>97847</v>
+        <v>97848</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
         <v>130341468</v>
       </c>
       <c r="B18" t="n">
-        <v>97844</v>
+        <v>97845</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>130340199</v>
       </c>
       <c r="B19" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>130334045</v>
       </c>
       <c r="B20" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130333964</v>
       </c>
       <c r="B21" t="n">
-        <v>97844</v>
+        <v>97845</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130340205</v>
       </c>
       <c r="B22" t="n">
-        <v>97847</v>
+        <v>97848</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>130332893</v>
       </c>
       <c r="B23" t="n">
-        <v>97841</v>
+        <v>97842</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>130341475</v>
       </c>
       <c r="B24" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>97847</v>
+        <v>97848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>130347969</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>130347955</v>
       </c>
       <c r="B27" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97847</v>
+        <v>97848</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>130347968</v>
       </c>
       <c r="B29" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>130340203</v>
       </c>
       <c r="B4" t="n">
-        <v>97848</v>
+        <v>97851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>130341464</v>
       </c>
       <c r="B5" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>130341476</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,53 +1321,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130341465</v>
+        <v>130340207</v>
       </c>
       <c r="B8" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510857</v>
+        <v>510840</v>
       </c>
       <c r="R8" t="n">
-        <v>6746077</v>
+        <v>6746211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,77 +1392,98 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130340207</v>
+        <v>130341465</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>57053</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510840</v>
+        <v>510857</v>
       </c>
       <c r="R9" t="n">
-        <v>6746211</v>
+        <v>6746077</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,45 +1513,29 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1772,7 +1772,7 @@
         <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>130334004</v>
       </c>
       <c r="B13" t="n">
-        <v>97848</v>
+        <v>97851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>130342663</v>
       </c>
       <c r="B14" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>130334159</v>
       </c>
       <c r="B15" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130334085</v>
+        <v>130340204</v>
       </c>
       <c r="B16" t="n">
-        <v>57053</v>
+        <v>97851</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,39 +2208,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510869</v>
+        <v>510879</v>
       </c>
       <c r="R16" t="n">
-        <v>6746060</v>
+        <v>6746058</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,7 +2267,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2282,7 +2277,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,22 +2292,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130340204</v>
+        <v>130334085</v>
       </c>
       <c r="B17" t="n">
-        <v>97848</v>
+        <v>57053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,34 +2315,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510879</v>
+        <v>510869</v>
       </c>
       <c r="R17" t="n">
-        <v>6746058</v>
+        <v>6746060</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,12 +2404,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2419,7 +2419,7 @@
         <v>130341468</v>
       </c>
       <c r="B18" t="n">
-        <v>97845</v>
+        <v>97848</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>130334045</v>
       </c>
       <c r="B20" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         <v>130333964</v>
       </c>
       <c r="B21" t="n">
-        <v>97845</v>
+        <v>97848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>130340205</v>
       </c>
       <c r="B22" t="n">
-        <v>97848</v>
+        <v>97851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2952,7 +2952,7 @@
         <v>130332893</v>
       </c>
       <c r="B23" t="n">
-        <v>97842</v>
+        <v>97845</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>130341475</v>
       </c>
       <c r="B24" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>97848</v>
+        <v>97851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>130347969</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97848</v>
+        <v>97851</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3559,7 +3559,7 @@
         <v>130347968</v>
       </c>
       <c r="B29" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B2" t="n">
-        <v>57053</v>
+        <v>97845</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R2" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B3" t="n">
-        <v>97845</v>
+        <v>57053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R3" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B11" t="n">
-        <v>57053</v>
+        <v>97845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,42 +1665,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R11" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,7 +1724,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1742,7 +1734,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,22 +1749,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B12" t="n">
-        <v>97845</v>
+        <v>57053</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,34 +1772,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R12" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130340204</v>
+        <v>130334085</v>
       </c>
       <c r="B16" t="n">
-        <v>97851</v>
+        <v>57053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,34 +2208,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510879</v>
+        <v>510869</v>
       </c>
       <c r="R16" t="n">
-        <v>6746058</v>
+        <v>6746060</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2267,7 +2272,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2277,7 +2282,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2292,22 +2297,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130334085</v>
+        <v>130340204</v>
       </c>
       <c r="B17" t="n">
-        <v>57053</v>
+        <v>97851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,39 +2320,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510869</v>
+        <v>510879</v>
       </c>
       <c r="R17" t="n">
-        <v>6746060</v>
+        <v>6746058</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,12 +2404,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130332854</v>
+        <v>130340201</v>
       </c>
       <c r="B2" t="n">
-        <v>97845</v>
+        <v>57053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510552</v>
+        <v>510874</v>
       </c>
       <c r="R2" t="n">
-        <v>6746150</v>
+        <v>6746081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +778,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130340201</v>
+        <v>130332854</v>
       </c>
       <c r="B3" t="n">
-        <v>57053</v>
+        <v>97845</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510874</v>
+        <v>510552</v>
       </c>
       <c r="R3" t="n">
-        <v>6746081</v>
+        <v>6746150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,12 +885,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130334091</v>
+        <v>130342662</v>
       </c>
       <c r="B11" t="n">
-        <v>97845</v>
+        <v>57053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,34 +1665,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510891</v>
+        <v>510863</v>
       </c>
       <c r="R11" t="n">
-        <v>6746058</v>
+        <v>6746072</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1734,7 +1742,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1749,22 +1757,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130342662</v>
+        <v>130334091</v>
       </c>
       <c r="B12" t="n">
-        <v>57053</v>
+        <v>97845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,42 +1780,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510863</v>
+        <v>510891</v>
       </c>
       <c r="R12" t="n">
-        <v>6746072</v>
+        <v>6746058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3056,45 +3056,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341475</v>
+        <v>130342664</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>97851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511192</v>
+        <v>510904</v>
       </c>
       <c r="R24" t="n">
-        <v>6746313</v>
+        <v>6746037</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,9 +3124,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,57 +3151,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130342664</v>
+        <v>130341475</v>
       </c>
       <c r="B25" t="n">
-        <v>97851</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510904</v>
+        <v>511192</v>
       </c>
       <c r="R25" t="n">
-        <v>6746037</v>
+        <v>6746313</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,19 +3231,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,12 +3248,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130340199</v>
+        <v>130334045</v>
       </c>
       <c r="B19" t="n">
-        <v>57053</v>
+        <v>97845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,42 +2524,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510881</v>
+        <v>510878</v>
       </c>
       <c r="R19" t="n">
-        <v>6746053</v>
+        <v>6746081</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2583,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2593,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,22 +2608,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130334045</v>
+        <v>130333964</v>
       </c>
       <c r="B20" t="n">
-        <v>97845</v>
+        <v>97848</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,16 +2631,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2663,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510878</v>
+        <v>510858</v>
       </c>
       <c r="R20" t="n">
-        <v>6746081</v>
+        <v>6746074</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2698,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2708,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130333964</v>
+        <v>130340199</v>
       </c>
       <c r="B21" t="n">
-        <v>97848</v>
+        <v>57053</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,34 +2738,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510858</v>
+        <v>510881</v>
       </c>
       <c r="R21" t="n">
-        <v>6746074</v>
+        <v>6746053</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,12 +2830,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -1109,53 +1109,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130340200</v>
+        <v>130341476</v>
       </c>
       <c r="B6" t="n">
-        <v>57053</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510881</v>
+        <v>510780</v>
       </c>
       <c r="R6" t="n">
-        <v>6746060</v>
+        <v>6746239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,19 +1177,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,57 +1194,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130341476</v>
+        <v>130340200</v>
       </c>
       <c r="B7" t="n">
-        <v>79221</v>
+        <v>57053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510780</v>
+        <v>510881</v>
       </c>
       <c r="R7" t="n">
-        <v>6746239</v>
+        <v>6746060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,9 +1282,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,12 +1309,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130334045</v>
+        <v>130340199</v>
       </c>
       <c r="B19" t="n">
-        <v>97845</v>
+        <v>57053</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,34 +2524,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510878</v>
+        <v>510881</v>
       </c>
       <c r="R19" t="n">
-        <v>6746081</v>
+        <v>6746053</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,7 +2591,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2593,7 +2601,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,22 +2616,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130333964</v>
+        <v>130334045</v>
       </c>
       <c r="B20" t="n">
-        <v>97848</v>
+        <v>97845</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,16 +2639,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2655,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510858</v>
+        <v>510878</v>
       </c>
       <c r="R20" t="n">
-        <v>6746074</v>
+        <v>6746081</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,7 +2698,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2708,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2727,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130340199</v>
+        <v>130333964</v>
       </c>
       <c r="B21" t="n">
-        <v>57053</v>
+        <v>97848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,42 +2746,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510881</v>
+        <v>510858</v>
       </c>
       <c r="R21" t="n">
-        <v>6746053</v>
+        <v>6746074</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2805,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,12 +2830,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3056,45 +3056,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130342664</v>
+        <v>130341475</v>
       </c>
       <c r="B24" t="n">
-        <v>97851</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>510904</v>
+        <v>511192</v>
       </c>
       <c r="R24" t="n">
-        <v>6746037</v>
+        <v>6746313</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,19 +3124,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,57 +3141,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130341475</v>
+        <v>130342664</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>97851</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>511192</v>
+        <v>510904</v>
       </c>
       <c r="R25" t="n">
-        <v>6746313</v>
+        <v>6746037</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,9 +3221,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,12 +3248,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130340201</v>
+        <v>130340207</v>
       </c>
       <c r="B2" t="n">
-        <v>57053</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510874</v>
+        <v>510840</v>
       </c>
       <c r="R2" t="n">
-        <v>6746081</v>
+        <v>6746211</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +758,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växte på gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,45 +791,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130332854</v>
+        <v>130341475</v>
       </c>
       <c r="B3" t="n">
-        <v>97845</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510552</v>
+        <v>511192</v>
       </c>
       <c r="R3" t="n">
-        <v>6746150</v>
+        <v>6746313</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,19 +859,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,57 +876,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130340203</v>
+        <v>130341476</v>
       </c>
       <c r="B4" t="n">
-        <v>97851</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510875</v>
+        <v>510780</v>
       </c>
       <c r="R4" t="n">
-        <v>6746032</v>
+        <v>6746239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,19 +956,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,62 +973,54 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130341464</v>
+        <v>130342665</v>
       </c>
       <c r="B5" t="n">
-        <v>57864</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510877</v>
+        <v>510961</v>
       </c>
       <c r="R5" t="n">
         <v>6746037</v>
@@ -1080,9 +1053,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,26 +1080,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130341476</v>
+        <v>130347967</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1140,17 +1123,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510780</v>
+        <v>510765</v>
       </c>
       <c r="R6" t="n">
-        <v>6746239</v>
+        <v>6745989</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,68 +1177,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130340200</v>
+        <v>130347968</v>
       </c>
       <c r="B7" t="n">
-        <v>57053</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510881</v>
+        <v>510802</v>
       </c>
       <c r="R7" t="n">
-        <v>6746060</v>
+        <v>6746015</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,19 +1257,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,26 +1274,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130340207</v>
+        <v>130347969</v>
       </c>
       <c r="B8" t="n">
-        <v>79221</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1350,22 +1315,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510840</v>
+        <v>510838</v>
       </c>
       <c r="R8" t="n">
-        <v>6746211</v>
+        <v>6746064</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,98 +1354,74 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växte på gran.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130341465</v>
+        <v>130341478</v>
       </c>
       <c r="B9" t="n">
-        <v>57053</v>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510857</v>
+        <v>510881</v>
       </c>
       <c r="R9" t="n">
-        <v>6746077</v>
+        <v>6746228</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,50 +1480,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130334033</v>
+        <v>130341477</v>
       </c>
       <c r="B10" t="n">
-        <v>57053</v>
+        <v>78334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510867</v>
+        <v>510880</v>
       </c>
       <c r="R10" t="n">
-        <v>6746073</v>
+        <v>6746230</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1615,19 +1548,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1642,44 +1565,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130342662</v>
+        <v>130341464</v>
       </c>
       <c r="B11" t="n">
-        <v>57053</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1687,20 +1610,20 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510863</v>
+        <v>510877</v>
       </c>
       <c r="R11" t="n">
-        <v>6746072</v>
+        <v>6746037</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,19 +1653,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,22 +1670,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130334091</v>
+        <v>130334033</v>
       </c>
       <c r="B12" t="n">
-        <v>97845</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,34 +1693,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510891</v>
+        <v>510867</v>
       </c>
       <c r="R12" t="n">
-        <v>6746058</v>
+        <v>6746073</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1839,7 +1757,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1767,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1794,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130334004</v>
+        <v>130334085</v>
       </c>
       <c r="B13" t="n">
-        <v>97851</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,34 +1805,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510871</v>
+        <v>510869</v>
       </c>
       <c r="R13" t="n">
-        <v>6746071</v>
+        <v>6746060</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1946,7 +1869,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1956,7 +1879,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1906,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130342663</v>
+        <v>130340198</v>
       </c>
       <c r="B14" t="n">
-        <v>97845</v>
+        <v>57141</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1994,34 +1917,50 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>510579</v>
+        <v>510881</v>
       </c>
       <c r="R14" t="n">
-        <v>6746019</v>
+        <v>6746233</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2053,7 +1992,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2063,7 +2002,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,22 +2017,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130334159</v>
+        <v>130340199</v>
       </c>
       <c r="B15" t="n">
-        <v>97845</v>
+        <v>57141</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2101,34 +2040,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>510877</v>
+        <v>510881</v>
       </c>
       <c r="R15" t="n">
-        <v>6746029</v>
+        <v>6746053</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,7 +2107,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2170,7 +2117,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2185,22 +2132,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130334085</v>
+        <v>130340200</v>
       </c>
       <c r="B16" t="n">
-        <v>57053</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2226,18 +2173,21 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>510869</v>
+        <v>510881</v>
       </c>
       <c r="R16" t="n">
         <v>6746060</v>
@@ -2272,7 +2222,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2282,7 +2232,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2297,22 +2247,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130340204</v>
+        <v>130340201</v>
       </c>
       <c r="B17" t="n">
-        <v>97851</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2320,34 +2270,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>510879</v>
+        <v>510874</v>
       </c>
       <c r="R17" t="n">
-        <v>6746058</v>
+        <v>6746081</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,7 +2337,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2389,7 +2347,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2416,10 +2374,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130341468</v>
+        <v>130341465</v>
       </c>
       <c r="B18" t="n">
-        <v>97848</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,34 +2385,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Grissen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>510864</v>
+        <v>510857</v>
       </c>
       <c r="R18" t="n">
-        <v>6746076</v>
+        <v>6746077</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2479,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130340199</v>
+        <v>130342662</v>
       </c>
       <c r="B19" t="n">
-        <v>57053</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2552,14 +2518,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>510881</v>
+        <v>510863</v>
       </c>
       <c r="R19" t="n">
-        <v>6746053</v>
+        <v>6746072</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2591,7 +2557,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2601,7 +2567,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,22 +2582,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130334045</v>
+        <v>130347955</v>
       </c>
       <c r="B20" t="n">
-        <v>97845</v>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,37 +2605,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grissmyren, Grissmyren, Dlr</t>
+          <t>Grissbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>510878</v>
+        <v>510724</v>
       </c>
       <c r="R20" t="n">
-        <v>6746081</v>
+        <v>6745987</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2696,19 +2662,9 @@
           <t>2025-12-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-29</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,22 +2679,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Erik Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130333964</v>
+        <v>130334004</v>
       </c>
       <c r="B21" t="n">
-        <v>97848</v>
+        <v>97989</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2746,16 +2702,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2770,10 +2726,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>510858</v>
+        <v>510871</v>
       </c>
       <c r="R21" t="n">
-        <v>6746074</v>
+        <v>6746071</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2805,7 +2761,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2815,7 +2771,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2842,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130340205</v>
+        <v>130334405</v>
       </c>
       <c r="B22" t="n">
-        <v>97851</v>
+        <v>97989</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2870,17 +2826,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grissen N om, Dlr</t>
+          <t>Grissmyren, Grissmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>510865</v>
+        <v>510883</v>
       </c>
       <c r="R22" t="n">
-        <v>6746076</v>
+        <v>6746021</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2912,7 +2882,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2922,7 +2892,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt spridd på cirka 15m x 10 m yta</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,22 +2912,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130332893</v>
+        <v>130340202</v>
       </c>
       <c r="B23" t="n">
-        <v>97845</v>
+        <v>97989</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2960,16 +2935,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2980,14 +2955,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>510545</v>
+        <v>510591</v>
       </c>
       <c r="R23" t="n">
-        <v>6746173</v>
+        <v>6746059</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,7 +2994,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3029,7 +3004,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,57 +3019,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Cecilia Rastad</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130341475</v>
+        <v>130340203</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>97989</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grissen, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>511192</v>
+        <v>510875</v>
       </c>
       <c r="R24" t="n">
-        <v>6746313</v>
+        <v>6746032</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3124,9 +3099,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,22 +3126,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130342664</v>
+        <v>130340204</v>
       </c>
       <c r="B25" t="n">
-        <v>97851</v>
+        <v>97989</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3184,14 +3169,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gryssen, Norr om, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>510904</v>
+        <v>510879</v>
       </c>
       <c r="R25" t="n">
-        <v>6746037</v>
+        <v>6746058</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3223,7 +3208,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3233,7 +3218,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,60 +3233,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kajsa Larsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130347969</v>
+        <v>130340205</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>97989</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Grissbäcken, Dlr</t>
+          <t>Grissen N om, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510838</v>
+        <v>510865</v>
       </c>
       <c r="R26" t="n">
-        <v>6746064</v>
+        <v>6746076</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3328,9 +3313,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3345,22 +3340,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130347955</v>
+        <v>130342664</v>
       </c>
       <c r="B27" t="n">
-        <v>57053</v>
+        <v>97989</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3368,37 +3363,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Grissbäcken, Dlr</t>
+          <t>Gryssen, Norr om, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>510724</v>
+        <v>510904</v>
       </c>
       <c r="R27" t="n">
-        <v>6745987</v>
+        <v>6746037</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3425,9 +3420,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3442,12 +3447,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Kajsa Larsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3457,7 +3462,7 @@
         <v>130347959</v>
       </c>
       <c r="B28" t="n">
-        <v>97851</v>
+        <v>97989</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3556,48 +3561,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130347968</v>
+        <v>130332793</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>97983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grissbäcken, Dlr</t>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>510802</v>
+        <v>510580</v>
       </c>
       <c r="R29" t="n">
-        <v>6746015</v>
+        <v>6746031</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3624,9 +3629,19 @@
           <t>2025-12-29</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,15 +3656,861 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erik Danielsson</t>
+          <t>Cecilia Rastad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130332854</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>510552</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6746150</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130332893</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kalkgruvan, Kalkgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>510545</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6746173</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130334045</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grissmyren, Grissmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>510878</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6746081</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130334091</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Grissmyren, Grissmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>510891</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6746058</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130334159</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Grissmyren, Grissmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>510877</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6746029</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130342663</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gryssen, Norr om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>510579</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6746019</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kajsa Larsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>130333964</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Grissmyren, Grissmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>510858</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6746074</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130341468</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grissen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>510864</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6746076</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61660-2025 artfynd.xlsx
+++ b/artfynd/A 61660-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340207</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341475</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130342665</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130347967</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130347968</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130347969</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1477,6 +1517,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341478</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1574,6 +1619,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341477</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341464</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334033</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1903,6 +1963,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334085</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2026,6 +2091,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340198</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2141,6 +2211,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340199</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2256,6 +2331,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340200</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2371,6 +2451,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340201</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2476,6 +2561,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341465</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2591,6 +2681,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130342662</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2688,6 +2783,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130347955</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2795,6 +2895,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334004</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2921,6 +3026,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334405</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3028,6 +3138,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340202</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3135,6 +3250,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340203</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3242,6 +3362,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340204</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3349,6 +3474,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130340205</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3456,6 +3586,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130342664</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3558,6 +3693,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130347959</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3665,6 +3805,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130332793</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3772,6 +3917,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130332854</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3879,6 +4029,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130332893</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3986,6 +4141,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334045</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4093,6 +4253,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334091</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4200,6 +4365,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130334159</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4307,6 +4477,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130342663</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4414,6 +4589,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130333964</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4511,8 +4691,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130341468</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>